--- a/jira_export_2026-08-17.xlsx
+++ b/jira_export_2026-08-17.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>215 h</t>
+          <t>216 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -3893,7 +3893,7 @@
         <v>3</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>3.38</v>
+        <v>3.88</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>3</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>3.38</v>
+        <v>3.88</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
@@ -7859,7 +7859,7 @@
         <v>16</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>1053.15</v>
       </c>
       <c r="P117" s="18" t="n">
-        <v>8.27</v>
+        <v>8.18</v>
       </c>
     </row>
   </sheetData>
@@ -9632,7 +9632,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>95.25</v>
+        <v>96.75</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>22</v>
@@ -9641,7 +9641,7 @@
         <v>5.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>123</v>
+        <v>124.5</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>35.5</v>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.7%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-08-17.xlsx
+++ b/jira_export_2026-08-17.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1,053 €</t>
+          <t>4,806 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>418 €</t>
+          <t>4,170 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>216 h</t>
+          <t>220 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Timon BOS</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -1468,8 +1468,8 @@
       <c r="N10" s="15" t="n">
         <v>2419</v>
       </c>
-      <c r="O10" s="16" t="n">
-        <v>0</v>
+      <c r="O10" s="15" t="n">
+        <v>2419</v>
       </c>
       <c r="P10" s="15" t="n">
         <v>0</v>
@@ -2669,7 +2669,7 @@
         <v>2</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>8.5</v>
+        <v>9.75</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
@@ -4052,11 +4052,11 @@
       <c r="N46" s="15" t="n">
         <v>910</v>
       </c>
-      <c r="O46" s="16" t="n">
-        <v>0</v>
+      <c r="O46" s="15" t="n">
+        <v>910</v>
       </c>
       <c r="P46" s="15" t="n">
-        <v>0</v>
+        <v>606.67</v>
       </c>
     </row>
     <row r="47">
@@ -4194,13 +4194,13 @@
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>1079</v>
-      </c>
-      <c r="O48" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O48" s="15" t="n">
+        <v>323.7</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>0</v>
+        <v>1294.8</v>
       </c>
     </row>
     <row r="49">
@@ -4905,10 +4905,10 @@
         <v>0</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P58" s="15" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="59">
@@ -7731,7 +7731,7 @@
         <v>15</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
@@ -8934,13 +8934,13 @@
       <c r="L117" s="17" t="inlineStr"/>
       <c r="M117" s="17" t="inlineStr"/>
       <c r="N117" s="18" t="n">
-        <v>67747.69399999999</v>
+        <v>66668.69399999999</v>
       </c>
       <c r="O117" s="18" t="n">
-        <v>1053.15</v>
+        <v>4805.85</v>
       </c>
       <c r="P117" s="18" t="n">
-        <v>8.18</v>
+        <v>36.82</v>
       </c>
     </row>
   </sheetData>
@@ -9632,7 +9632,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>96.75</v>
+        <v>98.5</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>22</v>
@@ -9641,7 +9641,7 @@
         <v>5.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>124.5</v>
+        <v>126.25</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>35.5</v>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -9778,16 +9778,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>389195</v>
+        <v>386762</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>145705</v>
+        <v>144183</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>243490</v>
+        <v>242580</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>152769</v>
+        <v>151859</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>21179</v>
@@ -9828,16 +9828,16 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>214484</v>
+        <v>212052</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>76115</v>
+        <v>74592</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>138370</v>
+        <v>137460</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>65480</v>
+        <v>64570</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>9871</v>

--- a/jira_export_2026-08-17.xlsx
+++ b/jira_export_2026-08-17.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>220 h</t>
+          <t>226 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P117"/>
+  <dimension ref="A1:P118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -4397,7 +4397,7 @@
         <v>4</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>219.36</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>87.73999999999999</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="52">
@@ -7381,7 +7381,7 @@
         <v>12</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
@@ -7406,12 +7406,12 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E94" s="14" t="n">
@@ -7444,23 +7444,23 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
         <v>13</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>1.19</v>
+        <v>0.25</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
@@ -7686,22 +7686,22 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
@@ -7719,34 +7719,34 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0.5</v>
+        <v>1.19</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O98" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="15" t="n">
@@ -7756,22 +7756,22 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7787,24 +7787,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H99" s="11" t="inlineStr"/>
+      <c r="H99" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K99" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L99" s="11" t="inlineStr"/>
-      <c r="M99" s="11" t="inlineStr"/>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O99" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7814,22 +7826,22 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
@@ -7845,11 +7857,7 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H100" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H100" s="14" t="inlineStr"/>
       <c r="I100" s="14" t="inlineStr">
         <is>
           <t>23/04/2025</t>
@@ -7859,18 +7867,10 @@
         <v>16</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="L100" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M100" s="14" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L100" s="14" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
       <c r="N100" s="15" t="n">
         <v>0</v>
       </c>
@@ -7884,12 +7884,12 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7917,34 +7917,34 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
         <v>16</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O101" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
@@ -7954,22 +7954,22 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -7982,27 +7982,39 @@
       </c>
       <c r="G102" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H102" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H102" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L102" s="14" t="inlineStr"/>
-      <c r="M102" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L102" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M102" s="14" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N102" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="15" t="n">
@@ -8012,22 +8024,22 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8040,35 +8052,23 @@
       </c>
       <c r="G103" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H103" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr"/>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L103" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M103" s="11" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L103" s="11" t="inlineStr"/>
+      <c r="M103" s="11" t="inlineStr"/>
       <c r="N103" s="12" t="n">
         <v>0</v>
       </c>
@@ -8082,12 +8082,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="G104" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H104" s="14" t="inlineStr">
@@ -8120,17 +8120,25 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L104" s="14" t="inlineStr"/>
-      <c r="M104" s="14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L104" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M104" s="14" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N104" s="15" t="n">
         <v>0</v>
       </c>
@@ -8144,12 +8152,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8159,7 +8167,7 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8182,14 +8190,14 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>1.5</v>
+        <v>5.75</v>
       </c>
       <c r="L105" s="11" t="inlineStr"/>
       <c r="M105" s="11" t="inlineStr"/>
@@ -8206,22 +8214,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8229,44 +8237,36 @@
       </c>
       <c r="F106" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G106" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M106" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L106" s="14" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
       <c r="N106" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O106" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="15" t="n">
@@ -8276,22 +8276,22 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G107" s="11" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
@@ -8325,16 +8325,16 @@
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O107" s="16" t="n">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H108" s="14" t="inlineStr">
@@ -8384,21 +8384,29 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L108" s="14" t="inlineStr"/>
-      <c r="M108" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L108" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M108" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N108" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O108" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="15" t="n">
@@ -8408,22 +8416,22 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8446,25 +8454,17 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K109" s="11" t="n">
         <v>2.5</v>
       </c>
-      <c r="L109" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M109" s="11" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+      <c r="L109" s="11" t="inlineStr"/>
+      <c r="M109" s="11" t="inlineStr"/>
       <c r="N109" s="12" t="n">
         <v>0</v>
       </c>
@@ -8478,22 +8478,22 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
@@ -8516,17 +8516,25 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L110" s="14" t="inlineStr"/>
-      <c r="M110" s="14" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L110" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M110" s="14" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N110" s="15" t="n">
         <v>0</v>
       </c>
@@ -8540,22 +8548,22 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8568,7 +8576,7 @@
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
@@ -8578,25 +8586,17 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L111" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M111" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L111" s="11" t="inlineStr"/>
+      <c r="M111" s="11" t="inlineStr"/>
       <c r="N111" s="12" t="n">
         <v>0</v>
       </c>
@@ -8610,22 +8610,22 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="G112" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-27990</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>406296</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
@@ -8680,12 +8680,12 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8718,17 +8718,25 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L113" s="11" t="inlineStr"/>
-      <c r="M113" s="11" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N113" s="12" t="n">
         <v>0</v>
       </c>
@@ -8742,28 +8750,26 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E114" s="14" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="n">
+        <v/>
       </c>
       <c r="F114" s="14" t="inlineStr">
         <is>
@@ -8777,7 +8783,7 @@
       </c>
       <c r="H114" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr">
@@ -8789,7 +8795,7 @@
         <v>35</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L114" s="14" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -8806,23 +8812,27 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C115" s="11" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -8837,19 +8847,19 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="L115" s="11" t="inlineStr"/>
       <c r="M115" s="11" t="inlineStr"/>
@@ -8866,21 +8876,25 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr"/>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E116" s="14" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E116" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -8888,20 +8902,24 @@
       </c>
       <c r="G116" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H116" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H116" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="L116" s="14" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -8916,31 +8934,83 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="17" t="inlineStr">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1326</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr"/>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr"/>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G117" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H117" s="11" t="inlineStr"/>
+      <c r="I117" s="11" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L117" s="11" t="inlineStr"/>
+      <c r="M117" s="11" t="inlineStr"/>
+      <c r="N117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B117" s="17" t="inlineStr"/>
-      <c r="C117" s="17" t="inlineStr"/>
-      <c r="D117" s="17" t="inlineStr"/>
-      <c r="E117" s="17" t="inlineStr"/>
-      <c r="F117" s="17" t="inlineStr"/>
-      <c r="G117" s="17" t="inlineStr"/>
-      <c r="H117" s="17" t="inlineStr"/>
-      <c r="I117" s="17" t="inlineStr"/>
-      <c r="J117" s="17" t="inlineStr"/>
-      <c r="K117" s="17" t="inlineStr"/>
-      <c r="L117" s="17" t="inlineStr"/>
-      <c r="M117" s="17" t="inlineStr"/>
-      <c r="N117" s="18" t="n">
+      <c r="B118" s="17" t="inlineStr"/>
+      <c r="C118" s="17" t="inlineStr"/>
+      <c r="D118" s="17" t="inlineStr"/>
+      <c r="E118" s="17" t="inlineStr"/>
+      <c r="F118" s="17" t="inlineStr"/>
+      <c r="G118" s="17" t="inlineStr"/>
+      <c r="H118" s="17" t="inlineStr"/>
+      <c r="I118" s="17" t="inlineStr"/>
+      <c r="J118" s="17" t="inlineStr"/>
+      <c r="K118" s="17" t="inlineStr"/>
+      <c r="L118" s="17" t="inlineStr"/>
+      <c r="M118" s="17" t="inlineStr"/>
+      <c r="N118" s="18" t="n">
         <v>66668.69399999999</v>
       </c>
-      <c r="O117" s="18" t="n">
+      <c r="O118" s="18" t="n">
         <v>4805.85</v>
       </c>
-      <c r="P117" s="18" t="n">
-        <v>36.82</v>
+      <c r="P118" s="18" t="n">
+        <v>36.54</v>
       </c>
     </row>
   </sheetData>
@@ -9058,6 +9128,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9632,7 +9703,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>98.5</v>
+        <v>99.5</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>22</v>
@@ -9641,17 +9712,17 @@
         <v>5.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>126.25</v>
+        <v>127.25</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>35.5</v>
+        <v>39.75</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>601.65</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.2%</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9764,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -9781,13 +9852,13 @@
         <v>386762</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>144183</v>
+        <v>142839</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>242580</v>
+        <v>243923</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>151859</v>
+        <v>153202</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>21179</v>
@@ -9806,13 +9877,13 @@
         <v>174711</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>69591</v>
+        <v>68247</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>105120</v>
+        <v>106464</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>87288</v>
+        <v>88632</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>11307</v>
